--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98125</v>
+        <v>17.12659</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73329</v>
+        <v>16.92069</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76936</v>
+        <v>16.9853</v>
       </c>
       <c r="F2" t="n">
-        <v>42.73338</v>
+        <v>43.07054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05124</v>
+        <v>0.05078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8144</v>
+        <v>1.83719</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.97731</v>
+        <v>17.17331</v>
       </c>
       <c r="D3" t="n">
-        <v>17.00449</v>
+        <v>16.54626</v>
       </c>
       <c r="E3" t="n">
-        <v>16.79764</v>
+        <v>16.8055</v>
       </c>
       <c r="F3" t="n">
-        <v>42.72922</v>
+        <v>42.7318</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05024</v>
+        <v>0.05201</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84363</v>
+        <v>1.87639</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84201</v>
+        <v>17.20816</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65478</v>
+        <v>16.66294</v>
       </c>
       <c r="E4" t="n">
-        <v>17.11608</v>
+        <v>16.93145</v>
       </c>
       <c r="F4" t="n">
-        <v>42.66514</v>
+        <v>43.07874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05116</v>
+        <v>0.05101</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8394</v>
+        <v>1.88627</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.01558</v>
+        <v>17.16474</v>
       </c>
       <c r="D5" t="n">
-        <v>16.45345</v>
+        <v>16.71957</v>
       </c>
       <c r="E5" t="n">
-        <v>16.72654</v>
+        <v>16.80289</v>
       </c>
       <c r="F5" t="n">
-        <v>42.87199</v>
+        <v>43.44884</v>
       </c>
       <c r="G5" t="n">
-        <v>0.052</v>
+        <v>0.05143</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86387</v>
+        <v>1.85636</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.26805</v>
+        <v>17.35162</v>
       </c>
       <c r="D6" t="n">
-        <v>16.93447</v>
+        <v>16.82765</v>
       </c>
       <c r="E6" t="n">
-        <v>17.08517</v>
+        <v>16.94683</v>
       </c>
       <c r="F6" t="n">
-        <v>43.66864</v>
+        <v>42.96849</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05042</v>
+        <v>0.05084</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8574</v>
+        <v>1.82561</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.00224</v>
+        <v>16.80843</v>
       </c>
       <c r="D7" t="n">
-        <v>16.58668</v>
+        <v>16.62756</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67615</v>
+        <v>16.69497</v>
       </c>
       <c r="F7" t="n">
-        <v>43.43502</v>
+        <v>42.10775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05104</v>
+        <v>0.05093</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86217</v>
+        <v>1.82252</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.34848</v>
+        <v>17.20471</v>
       </c>
       <c r="D8" t="n">
-        <v>17.01572</v>
+        <v>16.82734</v>
       </c>
       <c r="E8" t="n">
-        <v>17.02674</v>
+        <v>17.05377</v>
       </c>
       <c r="F8" t="n">
-        <v>42.69077</v>
+        <v>42.18597</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05131</v>
+        <v>0.05197</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84382</v>
+        <v>1.83281</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.02462</v>
+        <v>16.87692</v>
       </c>
       <c r="D9" t="n">
-        <v>16.61277</v>
+        <v>16.51744</v>
       </c>
       <c r="E9" t="n">
-        <v>16.88137</v>
+        <v>16.78567</v>
       </c>
       <c r="F9" t="n">
-        <v>43.35971</v>
+        <v>43.4748</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05102</v>
+        <v>0.05044</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84478</v>
+        <v>1.85672</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.00192</v>
+        <v>17.02881</v>
       </c>
       <c r="D10" t="n">
-        <v>16.83054</v>
+        <v>16.46061</v>
       </c>
       <c r="E10" t="n">
-        <v>17.16761</v>
+        <v>16.81214</v>
       </c>
       <c r="F10" t="n">
-        <v>43.1721</v>
+        <v>43.81928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05034</v>
+        <v>0.0519</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84562</v>
+        <v>1.82381</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.91979</v>
+        <v>17.12384</v>
       </c>
       <c r="D12" t="n">
-        <v>16.89099</v>
+        <v>16.91784</v>
       </c>
       <c r="E12" t="n">
-        <v>16.73383</v>
+        <v>16.92341</v>
       </c>
       <c r="F12" t="n">
-        <v>43.02787</v>
+        <v>42.76099</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05209</v>
+        <v>0.05118</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82321</v>
+        <v>1.88706</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.73117</v>
+        <v>17.10754</v>
       </c>
       <c r="D13" t="n">
-        <v>16.58383</v>
+        <v>16.77065</v>
       </c>
       <c r="E13" t="n">
-        <v>16.69422</v>
+        <v>16.99497</v>
       </c>
       <c r="F13" t="n">
-        <v>42.75988</v>
+        <v>41.88642</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05108</v>
+        <v>0.05292</v>
       </c>
       <c r="H13" t="n">
-        <v>1.84851</v>
+        <v>1.86554</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.95238</v>
+        <v>17.15011</v>
       </c>
       <c r="D14" t="n">
-        <v>16.92988</v>
+        <v>16.80451</v>
       </c>
       <c r="E14" t="n">
-        <v>16.93083</v>
+        <v>17.01019</v>
       </c>
       <c r="F14" t="n">
-        <v>42.81681</v>
+        <v>42.59197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05145</v>
+        <v>0.05215</v>
       </c>
       <c r="H14" t="n">
-        <v>1.88126</v>
+        <v>1.8433</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.16161</v>
+        <v>17.10658</v>
       </c>
       <c r="D15" t="n">
-        <v>16.9724</v>
+        <v>16.84859</v>
       </c>
       <c r="E15" t="n">
-        <v>17.05045</v>
+        <v>16.86458</v>
       </c>
       <c r="F15" t="n">
-        <v>43.13562</v>
+        <v>43.22388</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05095</v>
+        <v>0.05146</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85668</v>
+        <v>1.83164</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.09786</v>
+        <v>17.0538</v>
       </c>
       <c r="D16" t="n">
-        <v>16.60357</v>
+        <v>16.91827</v>
       </c>
       <c r="E16" t="n">
-        <v>16.8527</v>
+        <v>16.93726</v>
       </c>
       <c r="F16" t="n">
-        <v>43.02671</v>
+        <v>43.44102</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05101</v>
+        <v>0.0514</v>
       </c>
       <c r="H16" t="n">
-        <v>1.83471</v>
+        <v>1.84374</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.68503</v>
+        <v>16.91959</v>
       </c>
       <c r="D17" t="n">
-        <v>17.04781</v>
+        <v>16.81893</v>
       </c>
       <c r="E17" t="n">
-        <v>16.88522</v>
+        <v>16.91846</v>
       </c>
       <c r="F17" t="n">
-        <v>43.31082</v>
+        <v>43.3749</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04953</v>
+        <v>0.05073</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85538</v>
+        <v>1.84218</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.03065</v>
+        <v>17.12346</v>
       </c>
       <c r="D18" t="n">
-        <v>16.75128</v>
+        <v>16.66823</v>
       </c>
       <c r="E18" t="n">
-        <v>16.85488</v>
+        <v>16.87873</v>
       </c>
       <c r="F18" t="n">
-        <v>42.01803</v>
+        <v>43.21595</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05162</v>
+        <v>0.05017</v>
       </c>
       <c r="H18" t="n">
-        <v>1.84161</v>
+        <v>1.82465</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.05782</v>
+        <v>17.02102</v>
       </c>
       <c r="D19" t="n">
-        <v>16.94829</v>
+        <v>16.7974</v>
       </c>
       <c r="E19" t="n">
-        <v>16.83906</v>
+        <v>16.95017</v>
       </c>
       <c r="F19" t="n">
-        <v>42.33264</v>
+        <v>43.12555</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05092</v>
+        <v>0.05189</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84628</v>
+        <v>1.89821</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.99415</v>
+        <v>17.21009</v>
       </c>
       <c r="D20" t="n">
-        <v>17.15183</v>
+        <v>16.76311</v>
       </c>
       <c r="E20" t="n">
-        <v>17.15517</v>
+        <v>16.96103</v>
       </c>
       <c r="F20" t="n">
-        <v>43.10592</v>
+        <v>42.59386</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05095</v>
+        <v>0.05151</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85829</v>
+        <v>1.85683</v>
       </c>
     </row>
     <row r="21">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.616</v>
+        <v>0.59498</v>
       </c>
       <c r="D22" t="n">
-        <v>1.13754</v>
+        <v>1.13453</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.60854</v>
+        <v>0.61232</v>
       </c>
       <c r="D23" t="n">
-        <v>1.13025</v>
+        <v>1.11801</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.62683</v>
+        <v>0.61858</v>
       </c>
       <c r="D24" t="n">
-        <v>1.14025</v>
+        <v>1.13763</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.62046</v>
+        <v>0.61786</v>
       </c>
       <c r="D25" t="n">
-        <v>1.13125</v>
+        <v>1.1023</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.61019</v>
+        <v>0.6167</v>
       </c>
       <c r="D26" t="n">
-        <v>1.11509</v>
+        <v>1.11787</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.60767</v>
+        <v>0.60938</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1255</v>
+        <v>1.13497</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.62125</v>
+        <v>0.61288</v>
       </c>
       <c r="D28" t="n">
-        <v>1.12729</v>
+        <v>1.14528</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.60775</v>
+        <v>0.60701</v>
       </c>
       <c r="D29" t="n">
-        <v>1.12613</v>
+        <v>1.15199</v>
       </c>
     </row>
     <row r="30">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.61043</v>
+        <v>0.6062</v>
       </c>
       <c r="D30" t="n">
-        <v>1.12761</v>
+        <v>1.14732</v>
       </c>
     </row>
     <row r="31">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7579900000000001</v>
+        <v>0.75456</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08137</v>
+        <v>0.08119</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61556</v>
+        <v>0.60577</v>
       </c>
       <c r="F32" t="n">
-        <v>0.95441</v>
+        <v>0.96113</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11088</v>
+        <v>0.11072</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00754</v>
+        <v>0.00757</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09514</v>
+        <v>0.09538000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.13025</v>
+        <v>0.12889</v>
       </c>
     </row>
     <row r="33">
@@ -1159,28 +1159,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.76788</v>
+        <v>0.76034</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08168</v>
+        <v>0.08183</v>
       </c>
       <c r="E33" t="n">
-        <v>0.61017</v>
+        <v>0.6111799999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97603</v>
+        <v>0.97679</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1103</v>
+        <v>0.11336</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00778</v>
+        <v>0.00767</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09456000000000001</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12866</v>
+        <v>0.12722</v>
       </c>
     </row>
     <row r="34">
@@ -1190,28 +1190,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.77395</v>
+        <v>0.75169</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08115</v>
+        <v>0.08294</v>
       </c>
       <c r="E34" t="n">
-        <v>0.61102</v>
+        <v>0.62149</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96497</v>
+        <v>0.98575</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11241</v>
+        <v>0.10924</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00771</v>
+        <v>0.00768</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09357</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12917</v>
+        <v>0.12559</v>
       </c>
     </row>
     <row r="35">
@@ -1221,28 +1221,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7659</v>
+        <v>0.76896</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08144</v>
+        <v>0.08135000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.62557</v>
+        <v>0.6166</v>
       </c>
       <c r="F35" t="n">
-        <v>0.96005</v>
+        <v>0.95906</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1118</v>
+        <v>0.10975</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00772</v>
+        <v>0.00762</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09501999999999999</v>
+        <v>0.09377000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.13071</v>
+        <v>0.1267</v>
       </c>
     </row>
     <row r="36">
@@ -1252,28 +1252,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.76669</v>
+        <v>0.74586</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08391</v>
+        <v>0.08079</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61166</v>
+        <v>0.61335</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96317</v>
+        <v>0.96609</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1095</v>
+        <v>0.11102</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00764</v>
+        <v>0.00766</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09311</v>
+        <v>0.09556000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>0.13138</v>
+        <v>0.12518</v>
       </c>
     </row>
     <row r="37">
@@ -1283,28 +1283,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.76249</v>
+        <v>0.75929</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08159</v>
+        <v>0.08134</v>
       </c>
       <c r="E37" t="n">
-        <v>0.61535</v>
+        <v>0.61242</v>
       </c>
       <c r="F37" t="n">
-        <v>0.97684</v>
+        <v>0.97248</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10928</v>
+        <v>0.11044</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00768</v>
+        <v>0.00775</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09394</v>
+        <v>0.09123000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12705</v>
+        <v>0.12832</v>
       </c>
     </row>
     <row r="38">
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.76917</v>
+        <v>0.77466</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0842</v>
+        <v>0.0837</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6087900000000001</v>
+        <v>0.62924</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96512</v>
+        <v>0.9829</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11101</v>
+        <v>0.11029</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00771</v>
+        <v>0.00752</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0939</v>
+        <v>0.09325</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12576</v>
+        <v>0.12674</v>
       </c>
     </row>
     <row r="39">
@@ -1345,28 +1345,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.7516</v>
+        <v>0.7618</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0822</v>
+        <v>0.08055</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6196700000000001</v>
+        <v>0.60626</v>
       </c>
       <c r="F39" t="n">
-        <v>0.97441</v>
+        <v>0.97306</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10963</v>
+        <v>0.10825</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00765</v>
+        <v>0.00757</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0958</v>
+        <v>0.09447999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.12977</v>
+        <v>0.12764</v>
       </c>
     </row>
     <row r="40">
@@ -1376,28 +1376,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.75841</v>
+        <v>0.76436</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0813</v>
+        <v>0.07957</v>
       </c>
       <c r="E40" t="n">
-        <v>0.61549</v>
+        <v>0.61339</v>
       </c>
       <c r="F40" t="n">
-        <v>0.99072</v>
+        <v>0.96205</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11098</v>
+        <v>0.11055</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00754</v>
+        <v>0.00773</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09207</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>0.12662</v>
+        <v>0.12796</v>
       </c>
     </row>
   </sheetData>
